--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,6 +329,42 @@
   </si>
   <si>
     <t>Filière Obésité - Niveau 3 (Centre Spécialisé Obésité)</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Centre Ressources Autisme (CRA)</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Centre de référence des Troubles du Langage et de l’Apprentissage (CRTLA)</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Centre de référence du Trouble Déficit de l’Attention avec ou sans Hyperactivité (CRTDAH)</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Centre de compétence centre mémoire ressources et recherche (CMRR)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Centre expert Parkinson</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -663,7 +699,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -944,18 +980,66 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>36</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>105</v>
+      <c r="B42" t="s" s="2">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
